--- a/data/output/sim_gridrnd/ABS1/group_520_20/results/ABS1_G7_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_520_20/results/ABS1_G7_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G7_522_21_ABS1</t>
+          <t>S01_G7_519_22_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D2" t="n">
-        <v>31.13417346182357</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>514.9135569557067</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29.45355574120288</v>
-      </c>
-      <c r="K2" t="n">
-        <v>517.5857888197521</v>
-      </c>
-      <c r="L2" t="n">
-        <v>23.69940549873496</v>
-      </c>
-      <c r="M2" t="n">
-        <v>518.1035241846801</v>
-      </c>
-      <c r="N2" t="n">
-        <v>22.95514466862956</v>
-      </c>
-      <c r="O2" t="n">
-        <v>522.960702934787</v>
-      </c>
-      <c r="P2" t="n">
-        <v>26.64250136772095</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>520.1943464073527</v>
-      </c>
       <c r="R2" t="n">
-        <v>27.95125272097346</v>
+        <v>524.72</v>
       </c>
       <c r="S2" t="n">
-        <v>521.0290723205912</v>
+        <v>30.07</v>
       </c>
       <c r="T2" t="n">
-        <v>25.8320871308377</v>
+        <v>524.21</v>
       </c>
       <c r="U2" t="n">
-        <v>521.1212236120867</v>
+        <v>27.05</v>
       </c>
       <c r="V2" t="n">
-        <v>24.99197084801171</v>
+        <v>520.05</v>
       </c>
       <c r="W2" t="n">
-        <v>521.6076853926628</v>
+        <v>29.42</v>
       </c>
       <c r="X2" t="n">
-        <v>23.83325121586423</v>
+        <v>520.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>520.9900769796188</v>
+        <v>28.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.76663588313726</v>
+        <v>518.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1794871794871795</v>
+        <v>27.81</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2542372881355932</v>
+        <v>519.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3164556962025317</v>
+        <v>29.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3737373737373738</v>
+        <v>519.01</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.361344537815126</v>
+        <v>29.53</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3669064748201439</v>
+        <v>520.87</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3836477987421384</v>
+        <v>30.51</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3854748603351955</v>
+        <v>519.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.404040404040404</v>
+        <v>28.69</v>
       </c>
       <c r="AJ2" t="n">
-        <v>520.5</v>
+        <v>0.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>518.9666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="AL2" t="n">
-        <v>519.0125</v>
+        <v>0.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>520.8099999999999</v>
+        <v>0.26</v>
       </c>
       <c r="AN2" t="n">
-        <v>520.6</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="AO2" t="n">
-        <v>521.3571428571429</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AP2" t="n">
-        <v>521.40625</v>
+        <v>0.2125</v>
       </c>
       <c r="AQ2" t="n">
-        <v>521.1888888888889</v>
+        <v>0.2111111111111111</v>
       </c>
       <c r="AR2" t="n">
-        <v>521.2</v>
+        <v>0.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>43.6972539182956</v>
+        <v>525.725</v>
       </c>
       <c r="AT2" t="n">
-        <v>38.46252144043023</v>
+        <v>525.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>34.92473827747317</v>
+        <v>523.1375</v>
       </c>
       <c r="AV2" t="n">
-        <v>33.39930987310965</v>
+        <v>522.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>32.58639798034348</v>
+        <v>521.225</v>
       </c>
       <c r="AX2" t="n">
-        <v>32.03749397827744</v>
+        <v>520.9357142857143</v>
       </c>
       <c r="AY2" t="n">
-        <v>31.30101773005951</v>
+        <v>520.775</v>
       </c>
       <c r="AZ2" t="n">
-        <v>30.7897509803522</v>
+        <v>521.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>29.90334429457682</v>
+        <v>521.4450000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>458</v>
+        <v>32.14186327828553</v>
       </c>
       <c r="BC2" t="n">
-        <v>458</v>
+        <v>33.78125713074239</v>
       </c>
       <c r="BD2" t="n">
-        <v>458</v>
+        <v>33.47564179743235</v>
       </c>
       <c r="BE2" t="n">
-        <v>458</v>
+        <v>33.21990216722499</v>
       </c>
       <c r="BF2" t="n">
-        <v>458</v>
+        <v>32.65079440074927</v>
       </c>
       <c r="BG2" t="n">
-        <v>458</v>
+        <v>32.32429663675955</v>
       </c>
       <c r="BH2" t="n">
-        <v>458</v>
+        <v>32.25367227154143</v>
       </c>
       <c r="BI2" t="n">
-        <v>458</v>
+        <v>32.43857443093194</v>
       </c>
       <c r="BJ2" t="n">
-        <v>458</v>
+        <v>32.12190802240738</v>
       </c>
       <c r="BK2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BL2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BM2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BN2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BO2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BP2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BQ2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BR2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BS2" t="n">
-        <v>645</v>
+        <v>467</v>
       </c>
       <c r="BT2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>633</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>633</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>633</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>633</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CF2" t="n">
         <v>0</v>
       </c>
-      <c r="BU2" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.8518518518518519</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.9310344827586207</v>
+      <c r="CG2" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>519.51</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>28.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G7_519_22_ABS1</t>
+          <t>S02_G7_522_21_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D3" t="n">
-        <v>32.61675315048184</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>70.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>524.723664177576</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30.06909226687916</v>
-      </c>
-      <c r="K3" t="n">
-        <v>524.2066803365273</v>
-      </c>
-      <c r="L3" t="n">
-        <v>27.04762161690466</v>
-      </c>
-      <c r="M3" t="n">
-        <v>520.0500091529503</v>
-      </c>
-      <c r="N3" t="n">
-        <v>29.42360054188615</v>
-      </c>
-      <c r="O3" t="n">
-        <v>520.7517541773611</v>
-      </c>
-      <c r="P3" t="n">
-        <v>28.58429538705706</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>518.7572218039633</v>
-      </c>
       <c r="R3" t="n">
-        <v>27.80522786789987</v>
+        <v>514.91</v>
       </c>
       <c r="S3" t="n">
-        <v>519.855261639082</v>
+        <v>29.45</v>
       </c>
       <c r="T3" t="n">
-        <v>29.19954423736518</v>
+        <v>517.59</v>
       </c>
       <c r="U3" t="n">
-        <v>519.0137211210061</v>
+        <v>23.7</v>
       </c>
       <c r="V3" t="n">
-        <v>29.53241618194795</v>
+        <v>518.1</v>
       </c>
       <c r="W3" t="n">
-        <v>520.8654550965875</v>
+        <v>22.96</v>
       </c>
       <c r="X3" t="n">
-        <v>30.50928776906737</v>
+        <v>522.96</v>
       </c>
       <c r="Y3" t="n">
-        <v>519.5116052875079</v>
+        <v>26.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>28.68600092604372</v>
+        <v>520.1900000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6</v>
+        <v>27.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4333333333333333</v>
+        <v>521.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3</v>
+        <v>25.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.26</v>
+        <v>521.12</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2333333333333333</v>
+        <v>24.99</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2285714285714286</v>
+        <v>521.61</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2125</v>
+        <v>23.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2111111111111111</v>
+        <v>520.99</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.22</v>
+        <v>23.77</v>
       </c>
       <c r="AJ3" t="n">
-        <v>525.725</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="AK3" t="n">
-        <v>525.6</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="AL3" t="n">
-        <v>523.1375</v>
+        <v>0.3164556962025317</v>
       </c>
       <c r="AM3" t="n">
-        <v>522.09</v>
+        <v>0.3737373737373738</v>
       </c>
       <c r="AN3" t="n">
-        <v>521.225</v>
+        <v>0.361344537815126</v>
       </c>
       <c r="AO3" t="n">
-        <v>520.9357142857143</v>
+        <v>0.3669064748201439</v>
       </c>
       <c r="AP3" t="n">
-        <v>520.775</v>
+        <v>0.3836477987421384</v>
       </c>
       <c r="AQ3" t="n">
-        <v>521.5</v>
+        <v>0.3854748603351955</v>
       </c>
       <c r="AR3" t="n">
-        <v>521.4450000000001</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="AS3" t="n">
-        <v>32.14186327828553</v>
+        <v>520.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>33.78125713074239</v>
+        <v>518.9666666666667</v>
       </c>
       <c r="AU3" t="n">
-        <v>33.47564179743235</v>
+        <v>519.0125</v>
       </c>
       <c r="AV3" t="n">
-        <v>33.21990216722499</v>
+        <v>520.8099999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>32.65079440074927</v>
+        <v>520.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>32.32429663675955</v>
+        <v>521.3571428571429</v>
       </c>
       <c r="AY3" t="n">
-        <v>32.25367227154143</v>
+        <v>521.40625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>32.43857443093194</v>
+        <v>521.1888888888889</v>
       </c>
       <c r="BA3" t="n">
-        <v>32.12190802240738</v>
+        <v>521.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>467</v>
+        <v>43.6972539182956</v>
       </c>
       <c r="BC3" t="n">
-        <v>467</v>
+        <v>38.46252144043023</v>
       </c>
       <c r="BD3" t="n">
-        <v>467</v>
+        <v>34.92473827747317</v>
       </c>
       <c r="BE3" t="n">
-        <v>467</v>
+        <v>33.39930987310965</v>
       </c>
       <c r="BF3" t="n">
-        <v>467</v>
+        <v>32.58639798034348</v>
       </c>
       <c r="BG3" t="n">
-        <v>467</v>
+        <v>32.03749397827744</v>
       </c>
       <c r="BH3" t="n">
-        <v>467</v>
+        <v>31.30101773005951</v>
       </c>
       <c r="BI3" t="n">
-        <v>467</v>
+        <v>30.7897509803522</v>
       </c>
       <c r="BJ3" t="n">
-        <v>467</v>
+        <v>29.90334429457682</v>
       </c>
       <c r="BK3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BL3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BM3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BN3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BO3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BP3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BQ3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BR3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BS3" t="n">
-        <v>633</v>
+        <v>458</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.8</v>
+        <v>645</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.7142857142857143</v>
+        <v>645</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.5833333333333334</v>
+        <v>645</v>
       </c>
       <c r="BW3" t="n">
+        <v>645</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>645</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>645</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>645</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>645</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>645</v>
+      </c>
+      <c r="CC3" t="n">
         <v>0</v>
       </c>
-      <c r="BX3" t="n">
-        <v>0.631578947368421</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.7037037037037037</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.7666666666666667</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0.8529411764705882</v>
+      <c r="CD3" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>520.99</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>23.77</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>522</v>
       </c>
       <c r="C4" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D4" t="n">
         <v>19</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E4" t="n">
         <v>522</v>
@@ -1344,244 +1465,277 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>517.6405794930301</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25.06433539196555</v>
-      </c>
-      <c r="K4" t="n">
-        <v>520.1888329948014</v>
-      </c>
-      <c r="L4" t="n">
-        <v>22.99629435874434</v>
-      </c>
-      <c r="M4" t="n">
-        <v>521.4153851185373</v>
-      </c>
-      <c r="N4" t="n">
-        <v>21.23531653254823</v>
-      </c>
-      <c r="O4" t="n">
-        <v>521.9183104594423</v>
-      </c>
-      <c r="P4" t="n">
-        <v>22.94586479249572</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>520.9856196237065</v>
-      </c>
       <c r="R4" t="n">
-        <v>22.06699293120577</v>
+        <v>517.64</v>
       </c>
       <c r="S4" t="n">
-        <v>521.6840171286318</v>
+        <v>25.06</v>
       </c>
       <c r="T4" t="n">
-        <v>20.08616346370053</v>
+        <v>520.1900000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>521.5378882458652</v>
+        <v>23</v>
       </c>
       <c r="V4" t="n">
-        <v>20.60194238098885</v>
+        <v>521.42</v>
       </c>
       <c r="W4" t="n">
-        <v>520.2425246317412</v>
+        <v>21.24</v>
       </c>
       <c r="X4" t="n">
-        <v>20.84921960674604</v>
+        <v>521.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>521.3275279575965</v>
+        <v>22.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.58350724438597</v>
+        <v>520.99</v>
       </c>
       <c r="AA4" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>521.6799999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>521.54</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>520.24</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>521.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.7</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AK4" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AL4" t="n">
         <v>0.5189873417721519</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AM4" t="n">
         <v>0.5510204081632653</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AN4" t="n">
         <v>0.4915254237288136</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AO4" t="n">
         <v>0.4782608695652174</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AP4" t="n">
         <v>0.4777070063694268</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AQ4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AR4" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AS4" t="n">
         <v>527.3</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>520.9</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>521.675</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>522.15</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>521.225</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>521.0857142857143</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>520.5625</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>520.5</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>520.985</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>29.46794869005985</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>32.14327301318271</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>29.89639401332542</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>28.61201670627221</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>28.31150016630462</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>27.5772902725324</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>26.91274965049093</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>26.14436416855032</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>25.58837187083227</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>482</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>460</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>460</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>460</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>460</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>460</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>460</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>460</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>460</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>636</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BU4" t="n">
         <v>636</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BV4" t="n">
         <v>636</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BW4" t="n">
         <v>636</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BX4" t="n">
         <v>636</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BY4" t="n">
         <v>636</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BZ4" t="n">
         <v>636</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="CA4" t="n">
         <v>636</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="CB4" t="n">
         <v>636</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="CC4" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.7</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.9333333333333333</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>521.33</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>21.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G7_522_21_ABS1</t>
+          <t>S04_G7_522_20_ABS1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D5" t="n">
-        <v>31.13417346182357</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
         <v>522</v>
@@ -1590,720 +1744,819 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>61.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>523.6594820929332</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17.23864069583725</v>
-      </c>
-      <c r="K5" t="n">
-        <v>526.9445431665248</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13.27564232307251</v>
-      </c>
-      <c r="M5" t="n">
-        <v>520.2225464015251</v>
-      </c>
-      <c r="N5" t="n">
-        <v>19.82479835567059</v>
-      </c>
-      <c r="O5" t="n">
-        <v>522.5368387265072</v>
-      </c>
-      <c r="P5" t="n">
-        <v>22.54103197591202</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>522.4741846348319</v>
-      </c>
       <c r="R5" t="n">
-        <v>19.53781958828249</v>
+        <v>523.53</v>
       </c>
       <c r="S5" t="n">
-        <v>522.4658566136221</v>
+        <v>21.61</v>
       </c>
       <c r="T5" t="n">
-        <v>19.34810894503108</v>
+        <v>527.62</v>
       </c>
       <c r="U5" t="n">
-        <v>523.1690224717423</v>
+        <v>19.71</v>
       </c>
       <c r="V5" t="n">
-        <v>19.46225616818011</v>
+        <v>526.95</v>
       </c>
       <c r="W5" t="n">
-        <v>522.5914696117812</v>
+        <v>18.07</v>
       </c>
       <c r="X5" t="n">
-        <v>19.44850825482132</v>
+        <v>522.91</v>
       </c>
       <c r="Y5" t="n">
-        <v>521.95429471027</v>
+        <v>19.83</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.76371035059422</v>
+        <v>523.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.65</v>
+        <v>20.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7666666666666667</v>
+        <v>523.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.775</v>
+        <v>18.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.6530612244897959</v>
+        <v>521.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6440677966101694</v>
+        <v>20.37</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6521739130434783</v>
+        <v>522.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.6815286624203821</v>
+        <v>19.93</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.6571428571428571</v>
+        <v>523.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6701030927835051</v>
+        <v>21.37</v>
       </c>
       <c r="AJ5" t="n">
-        <v>527.275</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="AK5" t="n">
-        <v>527.55</v>
+        <v>0.6271186440677966</v>
       </c>
       <c r="AL5" t="n">
-        <v>525.2125</v>
+        <v>0.7215189873417721</v>
       </c>
       <c r="AM5" t="n">
-        <v>521.74</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="AN5" t="n">
-        <v>523.15</v>
+        <v>0.7288135593220338</v>
       </c>
       <c r="AO5" t="n">
-        <v>523.1785714285714</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="AP5" t="n">
-        <v>523.3125</v>
+        <v>0.6962025316455697</v>
       </c>
       <c r="AQ5" t="n">
-        <v>522.7833333333333</v>
+        <v>0.6966292134831461</v>
       </c>
       <c r="AR5" t="n">
-        <v>522.91</v>
+        <v>0.6868686868686869</v>
       </c>
       <c r="AS5" t="n">
-        <v>33.09077477183029</v>
+        <v>519.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>27.53145171133069</v>
+        <v>524.1333333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>25.78696073115248</v>
+        <v>525.4375</v>
       </c>
       <c r="AV5" t="n">
-        <v>25.47925430619978</v>
+        <v>524.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>25.50544059607675</v>
+        <v>523.725</v>
       </c>
       <c r="AX5" t="n">
-        <v>24.87347062265993</v>
+        <v>523.8285714285714</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.38113704793113</v>
+        <v>522.4625</v>
       </c>
       <c r="AZ5" t="n">
-        <v>24.0726389173361</v>
+        <v>522.6777777777778</v>
       </c>
       <c r="BA5" t="n">
-        <v>23.60724253274829</v>
+        <v>522.88</v>
       </c>
       <c r="BB5" t="n">
-        <v>471</v>
+        <v>42.11053906090493</v>
       </c>
       <c r="BC5" t="n">
-        <v>471</v>
+        <v>37.47597749077252</v>
       </c>
       <c r="BD5" t="n">
-        <v>471</v>
+        <v>33.63846152471899</v>
       </c>
       <c r="BE5" t="n">
-        <v>471</v>
+        <v>31.05688168506298</v>
       </c>
       <c r="BF5" t="n">
-        <v>471</v>
+        <v>29.81776945044683</v>
       </c>
       <c r="BG5" t="n">
-        <v>471</v>
+        <v>28.76876849669319</v>
       </c>
       <c r="BH5" t="n">
-        <v>471</v>
+        <v>27.92442647128138</v>
       </c>
       <c r="BI5" t="n">
-        <v>471</v>
+        <v>27.29136118008276</v>
       </c>
       <c r="BJ5" t="n">
-        <v>471</v>
+        <v>26.6511838386215</v>
       </c>
       <c r="BK5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BL5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BM5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BN5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BO5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BP5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BQ5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BR5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BS5" t="n">
-        <v>660</v>
+        <v>366</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.625</v>
+        <v>638</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.3076923076923077</v>
+        <v>638</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.9444444444444444</v>
+        <v>638</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.9523809523809523</v>
+        <v>638</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.8888888888888888</v>
+        <v>638</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.8125</v>
+        <v>638</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.8055555555555556</v>
+        <v>638</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.6829268292682927</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.7551020408163265</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>523.09</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>21.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G7_521_19_ABS1</t>
+          <t>S05_G7_522_21_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D6" t="n">
-        <v>28.16901408450704</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>527.0172899479597</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18.44009787398776</v>
-      </c>
-      <c r="K6" t="n">
-        <v>524.5706199817751</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19.4723296577111</v>
-      </c>
-      <c r="M6" t="n">
-        <v>519.715740421498</v>
-      </c>
-      <c r="N6" t="n">
-        <v>25.45956339240356</v>
-      </c>
-      <c r="O6" t="n">
-        <v>519.1083617283374</v>
-      </c>
-      <c r="P6" t="n">
-        <v>25.52703933365901</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>522.879070711244</v>
-      </c>
       <c r="R6" t="n">
-        <v>30.70419496518055</v>
+        <v>523.66</v>
       </c>
       <c r="S6" t="n">
-        <v>522.1888936067631</v>
+        <v>17.24</v>
       </c>
       <c r="T6" t="n">
-        <v>27.33287356972142</v>
+        <v>526.9400000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>522.1295101860949</v>
+        <v>13.28</v>
       </c>
       <c r="V6" t="n">
-        <v>26.10560816492324</v>
+        <v>520.22</v>
       </c>
       <c r="W6" t="n">
-        <v>522.9958041623114</v>
+        <v>19.82</v>
       </c>
       <c r="X6" t="n">
-        <v>24.99268182117284</v>
+        <v>522.54</v>
       </c>
       <c r="Y6" t="n">
-        <v>523.8570955189456</v>
+        <v>22.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.94348001462404</v>
+        <v>522.47</v>
       </c>
       <c r="AA6" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>522.47</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>523.17</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>522.59</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>0.65</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.3237410071942446</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.3743016759776536</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.3969849246231156</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>528.975</v>
-      </c>
       <c r="AK6" t="n">
-        <v>527.6333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>520.275</v>
+        <v>0.775</v>
       </c>
       <c r="AM6" t="n">
-        <v>520.5700000000001</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="AN6" t="n">
-        <v>521.775</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="AO6" t="n">
-        <v>522.1714285714286</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="AP6" t="n">
-        <v>522.1375</v>
+        <v>0.6815286624203821</v>
       </c>
       <c r="AQ6" t="n">
-        <v>522.3</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="AR6" t="n">
-        <v>522.14</v>
+        <v>0.6701030927835051</v>
       </c>
       <c r="AS6" t="n">
-        <v>33.12815079354716</v>
+        <v>527.275</v>
       </c>
       <c r="AT6" t="n">
-        <v>29.55614243360516</v>
+        <v>527.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>30.96771504325109</v>
+        <v>525.2125</v>
       </c>
       <c r="AV6" t="n">
-        <v>30.40041282614431</v>
+        <v>521.74</v>
       </c>
       <c r="AW6" t="n">
-        <v>30.16357143420962</v>
+        <v>523.15</v>
       </c>
       <c r="AX6" t="n">
-        <v>30.92131554610898</v>
+        <v>523.1785714285714</v>
       </c>
       <c r="AY6" t="n">
-        <v>30.46955191252408</v>
+        <v>523.3125</v>
       </c>
       <c r="AZ6" t="n">
-        <v>29.72277465737903</v>
+        <v>522.7833333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>28.9262925381045</v>
+        <v>522.91</v>
       </c>
       <c r="BB6" t="n">
-        <v>418</v>
+        <v>33.09077477183029</v>
       </c>
       <c r="BC6" t="n">
-        <v>418</v>
+        <v>27.53145171133069</v>
       </c>
       <c r="BD6" t="n">
-        <v>418</v>
+        <v>25.78696073115248</v>
       </c>
       <c r="BE6" t="n">
-        <v>418</v>
+        <v>25.47925430619978</v>
       </c>
       <c r="BF6" t="n">
-        <v>418</v>
+        <v>25.50544059607675</v>
       </c>
       <c r="BG6" t="n">
-        <v>418</v>
+        <v>24.87347062265993</v>
       </c>
       <c r="BH6" t="n">
-        <v>418</v>
+        <v>24.38113704793113</v>
       </c>
       <c r="BI6" t="n">
-        <v>418</v>
+        <v>24.0726389173361</v>
       </c>
       <c r="BJ6" t="n">
-        <v>418</v>
+        <v>23.60724253274829</v>
       </c>
       <c r="BK6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BL6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BM6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BN6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BO6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BP6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BQ6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BR6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BS6" t="n">
-        <v>626</v>
+        <v>471</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.7777777777777778</v>
+        <v>660</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.9166666666666666</v>
+        <v>660</v>
       </c>
       <c r="BV6" t="n">
-        <v>1</v>
+        <v>660</v>
       </c>
       <c r="BW6" t="n">
-        <v>1</v>
+        <v>660</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.9230769230769231</v>
+        <v>660</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.896551724137931</v>
+        <v>660</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.967741935483871</v>
+        <v>660</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.8857142857142857</v>
+        <v>660</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.9210526315789473</v>
+        <v>660</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>19.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S04_G7_522_20_ABS1</t>
+          <t>S06_G7_521_19_ABS1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D7" t="n">
-        <v>29.65159377316531</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>70.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>523.534524347552</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.60500350653772</v>
-      </c>
-      <c r="K7" t="n">
-        <v>527.6214188782225</v>
-      </c>
-      <c r="L7" t="n">
-        <v>19.71092759618612</v>
-      </c>
-      <c r="M7" t="n">
-        <v>526.9502789460951</v>
-      </c>
-      <c r="N7" t="n">
-        <v>18.07272666912369</v>
-      </c>
-      <c r="O7" t="n">
-        <v>522.9082043040404</v>
-      </c>
-      <c r="P7" t="n">
-        <v>19.8269443152432</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>523.5240255548342</v>
-      </c>
       <c r="R7" t="n">
-        <v>20.06882072055619</v>
+        <v>527.02</v>
       </c>
       <c r="S7" t="n">
-        <v>523.0272389506125</v>
+        <v>18.44</v>
       </c>
       <c r="T7" t="n">
-        <v>18.36426500995005</v>
+        <v>524.5700000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>521.4460202579772</v>
+        <v>19.47</v>
       </c>
       <c r="V7" t="n">
-        <v>20.36799220375139</v>
+        <v>519.72</v>
       </c>
       <c r="W7" t="n">
-        <v>522.2968090269687</v>
+        <v>25.46</v>
       </c>
       <c r="X7" t="n">
-        <v>19.92616422729933</v>
+        <v>519.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>523.0949601128663</v>
+        <v>25.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.36808421273678</v>
+        <v>522.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5897435897435898</v>
+        <v>30.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6271186440677966</v>
+        <v>522.1900000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.7215189873417721</v>
+        <v>27.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7373737373737373</v>
+        <v>522.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.7288135593220338</v>
+        <v>26.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.7246376811594203</v>
+        <v>523</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.6962025316455697</v>
+        <v>24.99</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.6966292134831461</v>
+        <v>523.86</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.6868686868686869</v>
+        <v>23.94</v>
       </c>
       <c r="AJ7" t="n">
-        <v>519.55</v>
+        <v>0.65</v>
       </c>
       <c r="AK7" t="n">
-        <v>524.1333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AL7" t="n">
-        <v>525.4375</v>
+        <v>0.35</v>
       </c>
       <c r="AM7" t="n">
-        <v>524.01</v>
+        <v>0.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>523.725</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO7" t="n">
-        <v>523.8285714285714</v>
+        <v>0.3237410071942446</v>
       </c>
       <c r="AP7" t="n">
-        <v>522.4625</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AQ7" t="n">
-        <v>522.6777777777778</v>
+        <v>0.3743016759776536</v>
       </c>
       <c r="AR7" t="n">
-        <v>522.88</v>
+        <v>0.3969849246231156</v>
       </c>
       <c r="AS7" t="n">
-        <v>42.11053906090493</v>
+        <v>528.975</v>
       </c>
       <c r="AT7" t="n">
-        <v>37.47597749077252</v>
+        <v>527.6333333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>33.63846152471899</v>
+        <v>520.275</v>
       </c>
       <c r="AV7" t="n">
-        <v>31.05688168506298</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>29.81776945044683</v>
+        <v>521.775</v>
       </c>
       <c r="AX7" t="n">
-        <v>28.76876849669319</v>
+        <v>522.1714285714286</v>
       </c>
       <c r="AY7" t="n">
-        <v>27.92442647128138</v>
+        <v>522.1375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27.29136118008276</v>
+        <v>522.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>26.6511838386215</v>
+        <v>522.14</v>
       </c>
       <c r="BB7" t="n">
-        <v>366</v>
+        <v>33.12815079354716</v>
       </c>
       <c r="BC7" t="n">
-        <v>366</v>
+        <v>29.55614243360516</v>
       </c>
       <c r="BD7" t="n">
-        <v>366</v>
+        <v>30.96771504325109</v>
       </c>
       <c r="BE7" t="n">
-        <v>366</v>
+        <v>30.40041282614431</v>
       </c>
       <c r="BF7" t="n">
-        <v>366</v>
+        <v>30.16357143420962</v>
       </c>
       <c r="BG7" t="n">
-        <v>366</v>
+        <v>30.92131554610898</v>
       </c>
       <c r="BH7" t="n">
-        <v>366</v>
+        <v>30.46955191252408</v>
       </c>
       <c r="BI7" t="n">
-        <v>366</v>
+        <v>29.72277465737903</v>
       </c>
       <c r="BJ7" t="n">
-        <v>366</v>
+        <v>28.9262925381045</v>
       </c>
       <c r="BK7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BL7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BM7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BN7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BO7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BP7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BQ7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BR7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BS7" t="n">
-        <v>638</v>
+        <v>418</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.75</v>
+        <v>626</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.6666666666666666</v>
+        <v>626</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.06666666666666667</v>
+        <v>626</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.04761904761904762</v>
+        <v>626</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.03703703703703703</v>
+        <v>626</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7878787878787878</v>
+        <v>626</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.6829268292682927</v>
+        <v>626</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.6956521739130435</v>
+        <v>626</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7551020408163265</v>
+        <v>626</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>523.86</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>23.94</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>519</v>
       </c>
       <c r="C8" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D8" t="n">
         <v>19</v>
-      </c>
-      <c r="D8" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E8" t="n">
         <v>519</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>507.3571837783173</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20.07855988775586</v>
-      </c>
-      <c r="K8" t="n">
-        <v>514.0307880459053</v>
-      </c>
-      <c r="L8" t="n">
-        <v>25.62650751782319</v>
-      </c>
-      <c r="M8" t="n">
-        <v>514.9640285530396</v>
-      </c>
-      <c r="N8" t="n">
-        <v>22.59655133600195</v>
-      </c>
-      <c r="O8" t="n">
-        <v>518.2222158629286</v>
-      </c>
-      <c r="P8" t="n">
-        <v>24.15745372445852</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>519.7010075309411</v>
-      </c>
       <c r="R8" t="n">
-        <v>26.40063916504858</v>
+        <v>507.36</v>
       </c>
       <c r="S8" t="n">
-        <v>520.1474345852114</v>
+        <v>20.08</v>
       </c>
       <c r="T8" t="n">
-        <v>26.67208032236628</v>
+        <v>514.03</v>
       </c>
       <c r="U8" t="n">
-        <v>520.173520143695</v>
+        <v>25.63</v>
       </c>
       <c r="V8" t="n">
-        <v>25.15838917003333</v>
+        <v>514.96</v>
       </c>
       <c r="W8" t="n">
-        <v>519.8812413053506</v>
+        <v>22.6</v>
       </c>
       <c r="X8" t="n">
-        <v>24.60518946161672</v>
+        <v>518.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>518.9639378258474</v>
+        <v>24.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.7928869258031</v>
+        <v>519.7</v>
       </c>
       <c r="AA8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>520.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>520.17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>519.88</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>518.96</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.25</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>0.175</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>0.26</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>0.2833333333333333</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>0.2428571428571429</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>0.2625</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>0.27</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>513.35</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>512.65</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>512.7375</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>515.03</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>516.6666666666666</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>516.7214285714285</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>517.26875</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>517.4555555555555</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>517.485</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>34.95822506935957</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>31.99365822575885</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>31.24129628792634</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>30.535374567868</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>29.90800710326398</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>29.80198168318506</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>29.5980831041049</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>29.04925361868131</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>28.57953419844347</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>461</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>461</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>461</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>461</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>461</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>461</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>461</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>461</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>461</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>646</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>646</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>646</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>646</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>646</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>646</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>646</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>646</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>646</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.76</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8275862068965517</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.84375</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>518.96</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>23.79</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>521</v>
       </c>
       <c r="C9" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D9" t="n">
         <v>20</v>
-      </c>
-      <c r="D9" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E9" t="n">
         <v>521</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>61.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>517.7538712422394</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14.13631465591329</v>
-      </c>
-      <c r="K9" t="n">
-        <v>520.8353246440511</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14.13150695104583</v>
-      </c>
-      <c r="M9" t="n">
-        <v>520.9707458018929</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14.8020086639998</v>
-      </c>
-      <c r="O9" t="n">
-        <v>521.463445143696</v>
-      </c>
-      <c r="P9" t="n">
-        <v>13.98582965851403</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>522.3278143314948</v>
-      </c>
       <c r="R9" t="n">
-        <v>16.27489883944145</v>
+        <v>517.75</v>
       </c>
       <c r="S9" t="n">
-        <v>521.2709939622953</v>
+        <v>14.14</v>
       </c>
       <c r="T9" t="n">
-        <v>15.7125726854054</v>
+        <v>520.84</v>
       </c>
       <c r="U9" t="n">
-        <v>521.2279060135628</v>
+        <v>14.13</v>
       </c>
       <c r="V9" t="n">
-        <v>16.27375463043922</v>
+        <v>520.97</v>
       </c>
       <c r="W9" t="n">
-        <v>522.1507045483988</v>
+        <v>14.8</v>
       </c>
       <c r="X9" t="n">
-        <v>16.2600927678385</v>
+        <v>521.46</v>
       </c>
       <c r="Y9" t="n">
-        <v>521.1300834728883</v>
+        <v>13.99</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.59832979279667</v>
+        <v>522.33</v>
       </c>
       <c r="AA9" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>521.27</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>521.23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>522.15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>0.65</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>0.68</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>0.7166666666666667</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0.6857142857142857</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.7206703910614525</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>519.775</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>523.05</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>521.0625</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>521.02</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>522.25</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>521.3214285714286</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>522.05625</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>522.4333333333333</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>522.1849999999999</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>25.94656769208598</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>24.59296986267959</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>23.07127204447124</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>21.76510050516652</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>21.17634293262177</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>20.8800204765714</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>20.60377601163194</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>20.39011198269069</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>20.05643973889683</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>483</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>483</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>483</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>483</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>483</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>483</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>483</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>483</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>483</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>640</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>640</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>640</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>640</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>640</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>640</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>640</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>640</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>640</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.625</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.65</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.7307692307692307</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.967741935483871</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>16.6</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>522</v>
       </c>
       <c r="C10" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D10" t="n">
         <v>19</v>
-      </c>
-      <c r="D10" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E10" t="n">
         <v>522</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>68.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>520.8985680796259</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24.27327291612604</v>
-      </c>
-      <c r="K10" t="n">
-        <v>521.0532315404738</v>
-      </c>
-      <c r="L10" t="n">
-        <v>23.57161561781576</v>
-      </c>
-      <c r="M10" t="n">
-        <v>520.9582241965982</v>
-      </c>
-      <c r="N10" t="n">
-        <v>28.71246910858657</v>
-      </c>
-      <c r="O10" t="n">
-        <v>520.5936269855948</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23.78076510444091</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>519.4749335740283</v>
-      </c>
       <c r="R10" t="n">
-        <v>23.68305547911926</v>
+        <v>520.9</v>
       </c>
       <c r="S10" t="n">
-        <v>518.6951441034915</v>
+        <v>24.27</v>
       </c>
       <c r="T10" t="n">
-        <v>22.08050405490592</v>
+        <v>521.05</v>
       </c>
       <c r="U10" t="n">
-        <v>517.8987852960587</v>
+        <v>23.57</v>
       </c>
       <c r="V10" t="n">
-        <v>21.81033571210988</v>
+        <v>520.96</v>
       </c>
       <c r="W10" t="n">
-        <v>517.568617728668</v>
+        <v>28.71</v>
       </c>
       <c r="X10" t="n">
-        <v>21.44270891231164</v>
+        <v>520.59</v>
       </c>
       <c r="Y10" t="n">
-        <v>518.527398673734</v>
+        <v>23.78</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.16032954904581</v>
+        <v>519.47</v>
       </c>
       <c r="AA10" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>518.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>517.5700000000001</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>518.53</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>0.4333333333333333</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>0.375</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>0.38</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>0.4</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>0.4244604316546763</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>0.4303797468354431</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>0.449438202247191</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>0.4747474747474748</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>514.325</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>517.2</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>519.4125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>519.55</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>519.6416666666667</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>519.6714285714286</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>519.40625</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>519.4388888888889</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>519.615</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>42.06862696832403</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>38.4494473302283</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>37.38271450483499</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>36.20424698844046</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>34.46926066157433</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>32.81407425766808</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>31.51077134786611</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>30.43392914511494</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>29.49994533893241</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>349</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>349</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>349</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>349</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>349</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>349</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>349</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>349</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>349</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>613</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>613</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>613</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>613</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>613</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>613</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>613</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>613</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>613</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.7741935483870968</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.8285714285714286</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.825</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.8409090909090909</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>518.53</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>20.16</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>521</v>
       </c>
       <c r="C11" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D11" t="n">
         <v>22</v>
-      </c>
-      <c r="D11" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E11" t="n">
         <v>521</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>66.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>529.6246656825866</v>
-      </c>
-      <c r="J11" t="n">
-        <v>25.53159076200337</v>
-      </c>
-      <c r="K11" t="n">
-        <v>524.468320859311</v>
-      </c>
-      <c r="L11" t="n">
-        <v>25.81315801527176</v>
-      </c>
-      <c r="M11" t="n">
-        <v>523.4833354567891</v>
-      </c>
-      <c r="N11" t="n">
-        <v>23.68132687679975</v>
-      </c>
-      <c r="O11" t="n">
-        <v>524.9491137595952</v>
-      </c>
-      <c r="P11" t="n">
-        <v>21.69705550618909</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>521.3799747091778</v>
-      </c>
       <c r="R11" t="n">
-        <v>23.51829333280777</v>
+        <v>529.62</v>
       </c>
       <c r="S11" t="n">
-        <v>520.3828714727555</v>
+        <v>25.53</v>
       </c>
       <c r="T11" t="n">
-        <v>23.3893429391012</v>
+        <v>524.47</v>
       </c>
       <c r="U11" t="n">
-        <v>518.8092490269913</v>
+        <v>25.81</v>
       </c>
       <c r="V11" t="n">
-        <v>25.14456993162912</v>
+        <v>523.48</v>
       </c>
       <c r="W11" t="n">
-        <v>519.4139949948079</v>
+        <v>23.68</v>
       </c>
       <c r="X11" t="n">
-        <v>24.56247428120048</v>
+        <v>524.95</v>
       </c>
       <c r="Y11" t="n">
-        <v>518.5686033743871</v>
+        <v>21.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.36675854379686</v>
+        <v>521.38</v>
       </c>
       <c r="AA11" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>520.38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>518.8099999999999</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>519.41</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>518.5700000000001</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AL11" t="n">
         <v>0.525</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AM11" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
         <v>0.5423728813559322</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
         <v>0.5507246376811594</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AP11" t="n">
         <v>0.5316455696202531</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AQ11" t="n">
         <v>0.4831460674157304</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
         <v>527.6</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>523.9166666666666</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>523.475</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>523.1799999999999</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>522.6166666666667</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>522.2928571428571</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>521.8125</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>521.4888888888889</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>521.04</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>28.80694360740133</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>31.1208888404914</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>29.69594879777375</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>28.31726681726186</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>27.85204460876955</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>27.44852231999057</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>26.86009761244363</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>26.94758057350293</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>27.1185987838605</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>480</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>475</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>475</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>475</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>475</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>475</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>475</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>475</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>475</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>623</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>623</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>623</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>623</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>623</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>623</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>623</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>623</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>623</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.84</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>1</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>518.5700000000001</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>23.37</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>521</v>
       </c>
       <c r="C12" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D12" t="n">
         <v>18</v>
-      </c>
-      <c r="D12" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E12" t="n">
         <v>521</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>64.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>518.4607867645457</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10.00461303051681</v>
-      </c>
-      <c r="K12" t="n">
-        <v>516.2019248656272</v>
-      </c>
-      <c r="L12" t="n">
-        <v>14.54149928700613</v>
-      </c>
-      <c r="M12" t="n">
-        <v>521.411571289569</v>
-      </c>
-      <c r="N12" t="n">
-        <v>22.36413531332889</v>
-      </c>
-      <c r="O12" t="n">
-        <v>520.1569241345632</v>
-      </c>
-      <c r="P12" t="n">
-        <v>19.50757180156555</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>519.2520883613479</v>
-      </c>
       <c r="R12" t="n">
-        <v>17.46285183872439</v>
+        <v>518.46</v>
       </c>
       <c r="S12" t="n">
-        <v>520.0139790489915</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>17.46474556773768</v>
+        <v>516.2</v>
       </c>
       <c r="U12" t="n">
-        <v>521.1251384022896</v>
+        <v>14.54</v>
       </c>
       <c r="V12" t="n">
-        <v>17.91267594222048</v>
+        <v>521.41</v>
       </c>
       <c r="W12" t="n">
-        <v>522.3085231401523</v>
+        <v>22.36</v>
       </c>
       <c r="X12" t="n">
-        <v>18.61285821935729</v>
+        <v>520.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>523.3839579695023</v>
+        <v>19.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.41960206094579</v>
+        <v>519.25</v>
       </c>
       <c r="AA12" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>520.01</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>521.13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>522.3099999999999</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>523.38</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
         <v>0.4576271186440678</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
         <v>0.5443037974683544</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
         <v>0.5353535353535354</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
         <v>0.559322033898305</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AO12" t="n">
         <v>0.5507246376811594</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AP12" t="n">
         <v>0.569620253164557</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
         <v>0.5480225988700564</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
         <v>0.5837563451776649</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
         <v>522.875</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>516.6833333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>521.2375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>521.67</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>521.2166666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>520.5857142857143</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>520.975</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>521.1777777777778</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>522.21</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>25.80425110325816</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>25.61802208515629</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>24.97811229356614</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>25.10061951426698</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>24.2916938250277</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>23.63501812211391</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>23.1430200060407</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>23.05962213132527</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>22.82621081125819</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>486</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>469</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>469</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>469</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>469</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>469</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>469</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>469</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>469</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>649</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>649</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>649</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>649</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>649</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>649</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>649</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>649</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>649</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.875</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.9117647058823529</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>523.38</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>19.42</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>519</v>
       </c>
       <c r="C13" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D13" t="n">
         <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E13" t="n">
         <v>519</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>528.024340127119</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17.84678631296565</v>
-      </c>
-      <c r="K13" t="n">
-        <v>525.6356944767742</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20.86933842050437</v>
-      </c>
-      <c r="M13" t="n">
-        <v>520.7267676710143</v>
-      </c>
-      <c r="N13" t="n">
-        <v>21.53859225199574</v>
-      </c>
-      <c r="O13" t="n">
-        <v>522.1724105804612</v>
-      </c>
-      <c r="P13" t="n">
-        <v>20.34431513148342</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>521.6954495291976</v>
-      </c>
       <c r="R13" t="n">
-        <v>18.72654799848782</v>
+        <v>528.02</v>
       </c>
       <c r="S13" t="n">
-        <v>521.9858962319106</v>
+        <v>17.85</v>
       </c>
       <c r="T13" t="n">
-        <v>17.06021086186374</v>
+        <v>525.64</v>
       </c>
       <c r="U13" t="n">
-        <v>520.5783287895106</v>
+        <v>20.87</v>
       </c>
       <c r="V13" t="n">
-        <v>17.38542839321908</v>
+        <v>520.73</v>
       </c>
       <c r="W13" t="n">
-        <v>518.4722081005623</v>
+        <v>21.54</v>
       </c>
       <c r="X13" t="n">
-        <v>18.81528237445305</v>
+        <v>522.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>517.0811678528643</v>
+        <v>20.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.117311762895</v>
+        <v>521.7</v>
       </c>
       <c r="AA13" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>521.99</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>520.58</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>518.47</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>517.08</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.7</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>0.55</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>0.5932203389830508</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>0.5797101449275363</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>0.6075949367088608</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>0.5730337078651685</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>0.5816326530612245</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>531.875</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>527.3</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>524.7875</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>524.49</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>524.3916666666667</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>523.7142857142857</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>523.66875</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>522.4222222222222</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>521.37</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>28.88701048914546</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>28.69105551677503</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>27.78654969135247</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>27.0260966474998</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>25.86416305538526</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>24.91020608800615</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>24.22259324344732</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>23.77345755145047</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>23.47728902577979</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>482</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>482</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>482</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>482</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>482</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>482</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>482</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>482</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>482</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>630</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>630</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>630</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>630</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>630</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>630</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>630</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>630</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>630</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>1</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.85</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.96</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.8064516129032258</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>517.08</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>21.12</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>520</v>
       </c>
       <c r="C14" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D14" t="n">
         <v>21</v>
-      </c>
-      <c r="D14" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E14" t="n">
         <v>520</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>70.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>529.4317784916177</v>
-      </c>
-      <c r="J14" t="n">
-        <v>31.6649971812299</v>
-      </c>
-      <c r="K14" t="n">
-        <v>530.5643703564376</v>
-      </c>
-      <c r="L14" t="n">
-        <v>29.36635050524248</v>
-      </c>
-      <c r="M14" t="n">
-        <v>530.2322361402049</v>
-      </c>
-      <c r="N14" t="n">
-        <v>32.9243577143282</v>
-      </c>
-      <c r="O14" t="n">
-        <v>528.0778553116994</v>
-      </c>
-      <c r="P14" t="n">
-        <v>30.57619134922957</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>523.7507174500813</v>
-      </c>
       <c r="R14" t="n">
-        <v>31.39748260214377</v>
+        <v>529.4299999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>522.2570090056718</v>
+        <v>31.66</v>
       </c>
       <c r="T14" t="n">
-        <v>30.20447436969306</v>
+        <v>530.5599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>519.4325848170234</v>
+        <v>29.37</v>
       </c>
       <c r="V14" t="n">
-        <v>27.41160668502603</v>
+        <v>530.23</v>
       </c>
       <c r="W14" t="n">
-        <v>521.3723260667596</v>
+        <v>32.92</v>
       </c>
       <c r="X14" t="n">
-        <v>26.27332250579066</v>
+        <v>528.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>521.5553339390772</v>
+        <v>30.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>27.29802186870184</v>
+        <v>523.75</v>
       </c>
       <c r="AA14" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>522.26</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>519.4299999999999</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>521.37</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>521.5599999999999</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>0.4358974358974359</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
         <v>0.5932203389830508</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AL14" t="n">
         <v>0.4683544303797468</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AM14" t="n">
         <v>0.4747474747474748</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AN14" t="n">
         <v>0.4117647058823529</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AO14" t="n">
         <v>0.3623188405797101</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AP14" t="n">
         <v>0.4050632911392405</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AQ14" t="n">
         <v>0.4204545454545455</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AR14" t="n">
         <v>0.4183673469387755</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AS14" t="n">
         <v>530.75</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>533.3</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>530.5875</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>529.86</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>528.9166666666666</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>527.8285714285714</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>528.65</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>527.8722222222223</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>526.47</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>43.48548608443971</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>39.36593281844934</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>38.38642134596555</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>36.96728824244483</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>36.36976384611567</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>35.790250639194</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>34.63672184257626</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>33.59894683461167</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>32.91943347021634</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>422</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>422</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>422</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>422</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>422</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>422</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>422</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>422</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>422</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>640</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>640</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>640</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>640</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>640</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>640</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>640</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>640</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>640</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.8709677419354839</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8529411764705882</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>521.5599999999999</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>27.3</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>519</v>
       </c>
       <c r="C15" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D15" t="n">
         <v>18</v>
-      </c>
-      <c r="D15" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E15" t="n">
         <v>519</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>62.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>517.1681445092042</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13.78337434371629</v>
-      </c>
-      <c r="K15" t="n">
-        <v>518.9235594668875</v>
-      </c>
-      <c r="L15" t="n">
-        <v>12.50520830351858</v>
-      </c>
-      <c r="M15" t="n">
-        <v>518.8389942621272</v>
-      </c>
-      <c r="N15" t="n">
-        <v>15.13592322545137</v>
-      </c>
-      <c r="O15" t="n">
-        <v>518.3944012009977</v>
-      </c>
-      <c r="P15" t="n">
-        <v>18.90299985566707</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>518.2259841719225</v>
-      </c>
       <c r="R15" t="n">
-        <v>17.80656828702686</v>
+        <v>517.17</v>
       </c>
       <c r="S15" t="n">
-        <v>519.4280588375477</v>
+        <v>13.78</v>
       </c>
       <c r="T15" t="n">
-        <v>19.57454029085225</v>
+        <v>518.92</v>
       </c>
       <c r="U15" t="n">
-        <v>518.7516846693005</v>
+        <v>12.51</v>
       </c>
       <c r="V15" t="n">
-        <v>19.23516422113369</v>
+        <v>518.84</v>
       </c>
       <c r="W15" t="n">
-        <v>519.8283024855596</v>
+        <v>15.14</v>
       </c>
       <c r="X15" t="n">
-        <v>18.24797354830946</v>
+        <v>518.39</v>
       </c>
       <c r="Y15" t="n">
-        <v>518.6133400110866</v>
+        <v>18.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.64543980603624</v>
+        <v>518.23</v>
       </c>
       <c r="AA15" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>519.4299999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>518.75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>519.83</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>518.61</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>0.7627118644067796</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AL15" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AM15" t="n">
         <v>0.6122448979591837</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AN15" t="n">
         <v>0.559322033898305</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AO15" t="n">
         <v>0.5797101449275363</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AP15" t="n">
         <v>0.5569620253164557</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AQ15" t="n">
         <v>0.5617977528089888</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AR15" t="n">
         <v>0.5959595959595959</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
         <v>507.775</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>514.4833333333333</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>514.725</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>515.11</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>515.4916666666667</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>516.8714285714286</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>516.59375</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>516.6</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>516.99</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>30.94146691739097</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>28.61089050616138</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>26.32155722976891</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>25.76311122516068</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>25.47842088033628</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>25.08922445340767</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>24.49318703103988</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>24.0819434431692</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>23.53295349079669</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>360</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>360</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>360</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>360</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>360</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>360</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>360</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>360</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>360</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>542</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>547</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>548</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>557</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>557</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>557</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>557</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>557</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>557</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.9310344827586207</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>1</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.972972972972973</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>518.61</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>17.65</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>522</v>
       </c>
       <c r="C16" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D16" t="n">
         <v>20</v>
-      </c>
-      <c r="D16" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E16" t="n">
         <v>522</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>64.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>535.4542585553203</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.32100802901315</v>
-      </c>
-      <c r="K16" t="n">
-        <v>532.5472915492412</v>
-      </c>
-      <c r="L16" t="n">
-        <v>17.74287122807629</v>
-      </c>
-      <c r="M16" t="n">
-        <v>530.8539944040239</v>
-      </c>
-      <c r="N16" t="n">
-        <v>19.51993820203267</v>
-      </c>
-      <c r="O16" t="n">
-        <v>530.1984633929446</v>
-      </c>
-      <c r="P16" t="n">
-        <v>20.07016903211056</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>528.3796803940498</v>
-      </c>
       <c r="R16" t="n">
-        <v>18.69772777610635</v>
+        <v>535.45</v>
       </c>
       <c r="S16" t="n">
-        <v>527.2541681705306</v>
+        <v>17.32</v>
       </c>
       <c r="T16" t="n">
-        <v>19.39024309962458</v>
+        <v>532.55</v>
       </c>
       <c r="U16" t="n">
-        <v>526.332866618267</v>
+        <v>17.74</v>
       </c>
       <c r="V16" t="n">
-        <v>19.42948280407892</v>
+        <v>530.85</v>
       </c>
       <c r="W16" t="n">
-        <v>526.0034561450159</v>
+        <v>19.52</v>
       </c>
       <c r="X16" t="n">
-        <v>18.60847323562088</v>
+        <v>530.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>526.1189694079692</v>
+        <v>20.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.00684854513395</v>
+        <v>528.38</v>
       </c>
       <c r="AA16" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>527.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>526.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>526</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>526.12</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>0.7</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>0.8</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>0.75</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>0.78</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>0.8</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0.8</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.7375</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.74</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>536.825</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>536.1833333333333</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>532.7875</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>531.9299999999999</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>532.1083333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>531.2285714285714</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>529.8625</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>529.6</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>529.77</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>30.64546255157523</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>27.57323077833926</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>26.39066773975225</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>25.3977380882629</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>24.7287942263445</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>24.02984538834478</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>24.27588502506139</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>24.2096399532638</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>23.95969741044323</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>488</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>488</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>488</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>488</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>488</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>488</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>488</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>488</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>488</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>637</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>637</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>637</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>637</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>637</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>637</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>637</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>637</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>637</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.9</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.8333333333333334</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>526.12</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>20.01</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>519</v>
       </c>
       <c r="C17" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D17" t="n">
         <v>22</v>
-      </c>
-      <c r="D17" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E17" t="n">
         <v>519</v>
@@ -4542,720 +5092,819 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>70.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>518.5229914480713</v>
-      </c>
-      <c r="J17" t="n">
-        <v>17.94285927187721</v>
-      </c>
-      <c r="K17" t="n">
-        <v>517.8898871124682</v>
-      </c>
-      <c r="L17" t="n">
-        <v>15.72344999514383</v>
-      </c>
-      <c r="M17" t="n">
-        <v>518.1572901006762</v>
-      </c>
-      <c r="N17" t="n">
-        <v>17.15529057373566</v>
-      </c>
-      <c r="O17" t="n">
-        <v>520.6017155047314</v>
-      </c>
-      <c r="P17" t="n">
-        <v>22.28374464189943</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>520.522973896817</v>
-      </c>
       <c r="R17" t="n">
-        <v>27.10926408775124</v>
+        <v>518.52</v>
       </c>
       <c r="S17" t="n">
-        <v>518.8628506719454</v>
+        <v>17.94</v>
       </c>
       <c r="T17" t="n">
-        <v>26.09644397157291</v>
+        <v>517.89</v>
       </c>
       <c r="U17" t="n">
-        <v>518.4834096160149</v>
+        <v>15.72</v>
       </c>
       <c r="V17" t="n">
-        <v>25.915779379546</v>
+        <v>518.16</v>
       </c>
       <c r="W17" t="n">
-        <v>518.8834913103881</v>
+        <v>17.16</v>
       </c>
       <c r="X17" t="n">
-        <v>26.67820081766967</v>
+        <v>520.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>517.0039824176473</v>
+        <v>22.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>27.68790936774841</v>
+        <v>520.52</v>
       </c>
       <c r="AA17" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>518.86</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>518.48</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>518.88</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>517</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AK17" t="n">
         <v>0.4333333333333333</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AL17" t="n">
         <v>0.425</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AM17" t="n">
         <v>0.48</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AN17" t="n">
         <v>0.4333333333333333</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AO17" t="n">
         <v>0.3428571428571429</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AP17" t="n">
         <v>0.2875</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AQ17" t="n">
         <v>0.2960893854748604</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AR17" t="n">
         <v>0.2525252525252525</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AS17" t="n">
         <v>523.2</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>518.0166666666667</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>518.05</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>520.21</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>521.05</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>519.45</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>519.125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>519.45</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>518.78</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>26.3658870512638</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>25.03496998644541</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>23.67852402494716</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>23.46115726045925</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>25.52771369838409</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>26.83636259150739</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>27.63076862846924</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>27.41294807608664</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>27.44961930519256</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>466</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>466</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>466</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>466</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>466</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>466</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>466</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>466</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>466</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>640</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>640</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>640</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>640</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>640</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>640</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>640</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>640</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>640</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.85</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>1</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.9117647058823529</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>517</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>27.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18_G7_519_19_ABS1</t>
+          <t>S17_G7_522_21_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D18" t="n">
-        <v>28.16901408450704</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>67.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>514.8458662068691</v>
-      </c>
-      <c r="J18" t="n">
-        <v>25.60759214622836</v>
-      </c>
-      <c r="K18" t="n">
-        <v>515.8518598362385</v>
-      </c>
-      <c r="L18" t="n">
-        <v>26.51532171791435</v>
-      </c>
-      <c r="M18" t="n">
-        <v>519.1095447229322</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27.9659274639928</v>
-      </c>
-      <c r="O18" t="n">
-        <v>518.149048862109</v>
-      </c>
-      <c r="P18" t="n">
-        <v>25.96075633165982</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>520.35607887794</v>
-      </c>
       <c r="R18" t="n">
-        <v>27.95734024946306</v>
+        <v>515.78</v>
       </c>
       <c r="S18" t="n">
-        <v>519.7076066034948</v>
+        <v>10.98</v>
       </c>
       <c r="T18" t="n">
-        <v>26.77640364276647</v>
+        <v>519.42</v>
       </c>
       <c r="U18" t="n">
-        <v>517.2646926425892</v>
+        <v>16.49</v>
       </c>
       <c r="V18" t="n">
-        <v>26.50558048911364</v>
+        <v>518.33</v>
       </c>
       <c r="W18" t="n">
-        <v>519.3608238650424</v>
+        <v>19.6</v>
       </c>
       <c r="X18" t="n">
-        <v>25.73584210052494</v>
+        <v>518.1799999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>519.6343748774113</v>
+        <v>18.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>25.74106610059746</v>
+        <v>516.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.3684210526315789</v>
+        <v>22.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.2758620689655172</v>
+        <v>517.0700000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2564102564102564</v>
+        <v>23.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2371134020618557</v>
+        <v>518.86</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1965811965811966</v>
+        <v>23.99</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1970802919708029</v>
+        <v>518.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1974522292993631</v>
+        <v>23.76</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1864406779661017</v>
+        <v>519.58</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.2244897959183673</v>
+        <v>24.58</v>
       </c>
       <c r="AJ18" t="n">
-        <v>519.775</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="AK18" t="n">
-        <v>519</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="AL18" t="n">
-        <v>519.5625</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="AM18" t="n">
-        <v>519.7</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="AN18" t="n">
-        <v>519.6083333333333</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="AO18" t="n">
-        <v>519.9857142857143</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="AP18" t="n">
-        <v>519.7875</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="AQ18" t="n">
-        <v>519.4277777777778</v>
+        <v>0.4597701149425287</v>
       </c>
       <c r="AR18" t="n">
-        <v>519.175</v>
+        <v>0.4432989690721649</v>
       </c>
       <c r="AS18" t="n">
-        <v>35.24804072569141</v>
+        <v>522.975</v>
       </c>
       <c r="AT18" t="n">
-        <v>35.21931288370062</v>
+        <v>522.0333333333333</v>
       </c>
       <c r="AU18" t="n">
-        <v>34.09613018731012</v>
+        <v>520.3</v>
       </c>
       <c r="AV18" t="n">
-        <v>32.73576026305178</v>
+        <v>519.9400000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>32.42537479437294</v>
+        <v>519.8583333333333</v>
       </c>
       <c r="AX18" t="n">
-        <v>32.2749318278102</v>
+        <v>519.1714285714286</v>
       </c>
       <c r="AY18" t="n">
-        <v>31.63056028194885</v>
+        <v>519.9625</v>
       </c>
       <c r="AZ18" t="n">
-        <v>31.02938223246468</v>
+        <v>519.7777777777778</v>
       </c>
       <c r="BA18" t="n">
-        <v>30.17307367505008</v>
+        <v>520.395</v>
       </c>
       <c r="BB18" t="n">
-        <v>465</v>
+        <v>24.34593138493576</v>
       </c>
       <c r="BC18" t="n">
-        <v>465</v>
+        <v>22.68844541954242</v>
       </c>
       <c r="BD18" t="n">
-        <v>465</v>
+        <v>22.6044243456895</v>
       </c>
       <c r="BE18" t="n">
-        <v>465</v>
+        <v>22.59682278551567</v>
       </c>
       <c r="BF18" t="n">
-        <v>465</v>
+        <v>22.65034798604403</v>
       </c>
       <c r="BG18" t="n">
-        <v>465</v>
+        <v>22.78876379056224</v>
       </c>
       <c r="BH18" t="n">
-        <v>465</v>
+        <v>23.83140981457035</v>
       </c>
       <c r="BI18" t="n">
-        <v>465</v>
+        <v>24.265557565212</v>
       </c>
       <c r="BJ18" t="n">
-        <v>465</v>
+        <v>25.18707952502632</v>
       </c>
       <c r="BK18" t="n">
-        <v>656</v>
+        <v>491</v>
       </c>
       <c r="BL18" t="n">
-        <v>656</v>
+        <v>483</v>
       </c>
       <c r="BM18" t="n">
-        <v>656</v>
+        <v>482</v>
       </c>
       <c r="BN18" t="n">
-        <v>656</v>
+        <v>482</v>
       </c>
       <c r="BO18" t="n">
-        <v>656</v>
+        <v>482</v>
       </c>
       <c r="BP18" t="n">
-        <v>656</v>
+        <v>482</v>
       </c>
       <c r="BQ18" t="n">
-        <v>656</v>
+        <v>475</v>
       </c>
       <c r="BR18" t="n">
-        <v>656</v>
+        <v>475</v>
       </c>
       <c r="BS18" t="n">
-        <v>656</v>
+        <v>475</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.8571428571428571</v>
+        <v>633</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.9</v>
+        <v>633</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.8571428571428571</v>
+        <v>633</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.9333333333333333</v>
+        <v>633</v>
       </c>
       <c r="BX18" t="n">
+        <v>633</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>633</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>633</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>633</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>633</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CG18" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CK18" t="n">
         <v>1</v>
       </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.896551724137931</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.9354838709677419</v>
+      <c r="CL18" t="n">
+        <v>519.58</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>24.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S17_G7_522_21_ABS1</t>
+          <t>S18_G7_519_19_ABS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D19" t="n">
-        <v>31.13417346182357</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>515.7817155659076</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10.98219454931447</v>
-      </c>
-      <c r="K19" t="n">
-        <v>519.4240216367151</v>
-      </c>
-      <c r="L19" t="n">
-        <v>16.49068195287724</v>
-      </c>
-      <c r="M19" t="n">
-        <v>518.3253678767834</v>
-      </c>
-      <c r="N19" t="n">
-        <v>19.59932751167312</v>
-      </c>
-      <c r="O19" t="n">
-        <v>518.1829284494853</v>
-      </c>
-      <c r="P19" t="n">
-        <v>18.97942829712028</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>516.7480956852881</v>
-      </c>
       <c r="R19" t="n">
-        <v>22.36948450608296</v>
+        <v>514.85</v>
       </c>
       <c r="S19" t="n">
-        <v>517.0694442437039</v>
+        <v>25.61</v>
       </c>
       <c r="T19" t="n">
-        <v>23.4005169980809</v>
+        <v>515.85</v>
       </c>
       <c r="U19" t="n">
-        <v>518.8590299055674</v>
+        <v>26.52</v>
       </c>
       <c r="V19" t="n">
-        <v>23.9901140027982</v>
+        <v>519.11</v>
       </c>
       <c r="W19" t="n">
-        <v>518.1472999177552</v>
+        <v>27.97</v>
       </c>
       <c r="X19" t="n">
-        <v>23.76170554993622</v>
+        <v>518.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>519.5819125542655</v>
+        <v>25.96</v>
       </c>
       <c r="Z19" t="n">
-        <v>24.58333879992917</v>
+        <v>520.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.7435897435897436</v>
+        <v>27.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.7241379310344828</v>
+        <v>519.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.6153846153846154</v>
+        <v>26.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.5876288659793815</v>
+        <v>517.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5689655172413793</v>
+        <v>26.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5373134328358209</v>
+        <v>519.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5064935064935064</v>
+        <v>25.74</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.4597701149425287</v>
+        <v>519.63</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.4432989690721649</v>
+        <v>25.74</v>
       </c>
       <c r="AJ19" t="n">
-        <v>522.975</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="AK19" t="n">
-        <v>522.0333333333333</v>
+        <v>0.2758620689655172</v>
       </c>
       <c r="AL19" t="n">
-        <v>520.3</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="AM19" t="n">
-        <v>519.9400000000001</v>
+        <v>0.2371134020618557</v>
       </c>
       <c r="AN19" t="n">
-        <v>519.8583333333333</v>
+        <v>0.1965811965811966</v>
       </c>
       <c r="AO19" t="n">
-        <v>519.1714285714286</v>
+        <v>0.1970802919708029</v>
       </c>
       <c r="AP19" t="n">
-        <v>519.9625</v>
+        <v>0.1974522292993631</v>
       </c>
       <c r="AQ19" t="n">
-        <v>519.7777777777778</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="AR19" t="n">
-        <v>520.395</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="AS19" t="n">
-        <v>24.34593138493576</v>
+        <v>519.775</v>
       </c>
       <c r="AT19" t="n">
-        <v>22.68844541954242</v>
+        <v>519</v>
       </c>
       <c r="AU19" t="n">
-        <v>22.6044243456895</v>
+        <v>519.5625</v>
       </c>
       <c r="AV19" t="n">
-        <v>22.59682278551567</v>
+        <v>519.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>22.65034798604403</v>
+        <v>519.6083333333333</v>
       </c>
       <c r="AX19" t="n">
-        <v>22.78876379056224</v>
+        <v>519.9857142857143</v>
       </c>
       <c r="AY19" t="n">
-        <v>23.83140981457035</v>
+        <v>519.7875</v>
       </c>
       <c r="AZ19" t="n">
-        <v>24.265557565212</v>
+        <v>519.4277777777778</v>
       </c>
       <c r="BA19" t="n">
-        <v>25.18707952502632</v>
+        <v>519.175</v>
       </c>
       <c r="BB19" t="n">
-        <v>491</v>
+        <v>35.24804072569141</v>
       </c>
       <c r="BC19" t="n">
-        <v>483</v>
+        <v>35.21931288370062</v>
       </c>
       <c r="BD19" t="n">
-        <v>482</v>
+        <v>34.09613018731012</v>
       </c>
       <c r="BE19" t="n">
-        <v>482</v>
+        <v>32.73576026305178</v>
       </c>
       <c r="BF19" t="n">
-        <v>482</v>
+        <v>32.42537479437294</v>
       </c>
       <c r="BG19" t="n">
-        <v>482</v>
+        <v>32.2749318278102</v>
       </c>
       <c r="BH19" t="n">
-        <v>475</v>
+        <v>31.63056028194885</v>
       </c>
       <c r="BI19" t="n">
-        <v>475</v>
+        <v>31.02938223246468</v>
       </c>
       <c r="BJ19" t="n">
-        <v>475</v>
+        <v>30.17307367505008</v>
       </c>
       <c r="BK19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BL19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BM19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BN19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BO19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BP19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BQ19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BR19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BS19" t="n">
-        <v>633</v>
+        <v>465</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.875</v>
+        <v>656</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.08333333333333333</v>
+        <v>656</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.6923076923076923</v>
+        <v>656</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.8</v>
+        <v>656</v>
       </c>
       <c r="BX19" t="n">
+        <v>656</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>656</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>656</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>656</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>656</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CG19" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0.967741935483871</v>
-      </c>
-      <c r="CB19" t="n">
+      <c r="CH19" t="n">
         <v>1</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>519.63</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>25.74</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>521</v>
       </c>
       <c r="C20" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D20" t="n">
         <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E20" t="n">
         <v>521</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ABS1</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>522.8200000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>521.04</v>
+      </c>
+      <c r="U20" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="V20" t="n">
+        <v>523.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="X20" t="n">
+        <v>522.36</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>522.49</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>524.1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>523.02</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>523.38</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.5949367088607594</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.5353535353535354</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.5042735042735043</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.5474452554744526</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.5641025641025641</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.5747126436781609</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.5876288659793815</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>529.125</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>524.5333333333333</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>524.53</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>524.1666666666666</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>524.2714285714286</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>524.44375</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>524.3944444444444</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>524.285</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>30.22762602322584</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>28.27924248553266</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>27.63874092646045</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>27.71153369988749</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>27.61078694198257</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>26.65516376055568</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>26.29941702657114</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>25.7026797613319</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>25.35120855107306</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>469</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>648</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>648</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>648</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>648</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CG20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ABS1</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>522.8237769434779</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16.62004532211103</v>
-      </c>
-      <c r="K20" t="n">
-        <v>521.0402088013676</v>
-      </c>
-      <c r="L20" t="n">
-        <v>20.16267895049011</v>
-      </c>
-      <c r="M20" t="n">
-        <v>523.0352751330307</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20.51291290635888</v>
-      </c>
-      <c r="O20" t="n">
-        <v>522.3554296213493</v>
-      </c>
-      <c r="P20" t="n">
-        <v>23.60698366446734</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>522.0986359515181</v>
-      </c>
-      <c r="R20" t="n">
-        <v>22.68245500866476</v>
-      </c>
-      <c r="S20" t="n">
-        <v>522.4856512164582</v>
-      </c>
-      <c r="T20" t="n">
-        <v>22.31238080090867</v>
-      </c>
-      <c r="U20" t="n">
-        <v>524.095438619398</v>
-      </c>
-      <c r="V20" t="n">
-        <v>21.25645269754537</v>
-      </c>
-      <c r="W20" t="n">
-        <v>523.0242186422569</v>
-      </c>
-      <c r="X20" t="n">
-        <v>20.98201037058044</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>523.3813543192124</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>20.28926073906839</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.5932203389830508</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.5949367088607594</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.5353535353535354</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.5042735042735043</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.5474452554744526</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.5641025641025641</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.5747126436781609</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.5876288659793815</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>529.125</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>524.5333333333333</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>524.5</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>524.53</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>524.1666666666666</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>524.2714285714286</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>524.44375</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>524.3944444444444</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>524.285</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>30.22762602322584</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>28.27924248553266</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>27.63874092646045</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>27.71153369988749</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>27.61078694198257</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>26.65516376055568</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>26.29941702657114</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>25.7026797613319</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>25.35120855107306</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>469</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>648</v>
-      </c>
-      <c r="BT20" t="n">
+      <c r="CH20" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.59375</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.6388888888888888</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.6842105263157895</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>523.38</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>20.29</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>519</v>
       </c>
       <c r="C21" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D21" t="n">
         <v>21</v>
-      </c>
-      <c r="D21" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E21" t="n">
         <v>519</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>516.716103357297</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24.56814305588783</v>
-      </c>
-      <c r="K21" t="n">
-        <v>516.9296178793289</v>
-      </c>
-      <c r="L21" t="n">
-        <v>26.0983521564441</v>
-      </c>
-      <c r="M21" t="n">
-        <v>517.9422610761841</v>
-      </c>
-      <c r="N21" t="n">
-        <v>26.13547407364036</v>
-      </c>
-      <c r="O21" t="n">
-        <v>520.0558090292523</v>
-      </c>
-      <c r="P21" t="n">
-        <v>26.36994066621768</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>520.0556357639116</v>
-      </c>
       <c r="R21" t="n">
-        <v>23.474981152675</v>
+        <v>516.72</v>
       </c>
       <c r="S21" t="n">
-        <v>518.9710187835417</v>
+        <v>24.57</v>
       </c>
       <c r="T21" t="n">
-        <v>22.32052275771873</v>
+        <v>516.9299999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>520.679861475166</v>
+        <v>26.1</v>
       </c>
       <c r="V21" t="n">
-        <v>25.33742504969867</v>
+        <v>517.9400000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>521.3299437846071</v>
+        <v>26.14</v>
       </c>
       <c r="X21" t="n">
-        <v>23.9553883415216</v>
+        <v>520.0599999999999</v>
       </c>
       <c r="Y21" t="n">
-        <v>521.0118637242899</v>
+        <v>26.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.86645248129634</v>
+        <v>520.0599999999999</v>
       </c>
       <c r="AA21" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>518.97</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>520.6799999999999</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>521.33</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>521.01</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>0.3949579831932773</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>0.4676258992805755</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>0.4842767295597484</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>0.4943820224719101</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>0.494949494949495</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>514.725</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>514.35</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>516.1625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>517.3</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>517.975</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>518.7357142857143</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>519.58125</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>519.7777777777778</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>519.705</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>42.01606091722545</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>39.91233101018614</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>38.04551345099709</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>35.57513176363511</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>33.7276994224826</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>32.24252088564454</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>31.16898937144899</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>30.4482357736601</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>29.64503288917049</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>358</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>358</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>358</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>358</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>358</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>358</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>358</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>358</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>358</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>646</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>646</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>646</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>646</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>646</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>646</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>646</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>646</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>646</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>1</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>1</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>1</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.96875</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9111111111111111</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>521.01</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>22.87</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>520.6</v>
       </c>
       <c r="C22" t="n">
+        <v>29.5774647887324</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.95</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.5774647887324</v>
       </c>
       <c r="E22" t="n">
         <v>520.6</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4235</v>
+      </c>
       <c r="I22" t="n">
-        <v>521.2176573883478</v>
+        <v>2.4015</v>
       </c>
       <c r="J22" t="n">
-        <v>20.61160384705348</v>
+        <v>2.3785</v>
       </c>
       <c r="K22" t="n">
-        <v>521.8256992624214</v>
+        <v>2.3585</v>
       </c>
       <c r="L22" t="n">
-        <v>20.76803808352638</v>
+        <v>2.3405</v>
       </c>
       <c r="M22" t="n">
-        <v>521.2733560455076</v>
+        <v>2.3255</v>
       </c>
       <c r="N22" t="n">
-        <v>22.48076926910938</v>
+        <v>2.4465</v>
       </c>
       <c r="O22" t="n">
-        <v>521.6878780084942</v>
+        <v>2.450499999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>22.81454409685556</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>521.1391769481825</v>
-      </c>
+        <v>2.437</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>23.28479495588208</v>
+        <v>521.2165</v>
       </c>
       <c r="S22" t="n">
-        <v>520.9391233598426</v>
+        <v>20.611</v>
       </c>
       <c r="T22" t="n">
-        <v>22.63090123596019</v>
+        <v>521.8254999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>520.6064940965105</v>
+        <v>20.7685</v>
       </c>
       <c r="V22" t="n">
-        <v>22.69144725281974</v>
+        <v>521.2735000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>520.9172449978689</v>
+        <v>22.481</v>
       </c>
       <c r="X22" t="n">
-        <v>22.40503176908513</v>
+        <v>521.688</v>
       </c>
       <c r="Y22" t="n">
-        <v>520.7645920493494</v>
+        <v>22.815</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.48424874876585</v>
+        <v>521.1395</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.582972334682861</v>
+        <v>23.285</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.5360734463276836</v>
+        <v>520.9399999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.4951829763063941</v>
+        <v>22.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.4961198179990521</v>
+        <v>520.6065000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.4878265756391723</v>
+        <v>22.692</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.4821416831397968</v>
+        <v>520.917</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.4813005092375421</v>
+        <v>22.4055</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.479630891415333</v>
+        <v>520.7634999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.4882816311462414</v>
+        <v>22.485</v>
       </c>
       <c r="AJ22" t="n">
-        <v>523.21375</v>
+        <v>0.583</v>
       </c>
       <c r="AK22" t="n">
-        <v>522.3741666666666</v>
+        <v>0.5355</v>
       </c>
       <c r="AL22" t="n">
-        <v>521.706875</v>
+        <v>0.4955</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.4820000000000001</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.4795000000000001</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>523.2144999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>522.3735</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>521.707</v>
+      </c>
+      <c r="AV22" t="n">
         <v>521.7445</v>
       </c>
-      <c r="AN22" t="n">
-        <v>521.8829166666667</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>521.7203571428571</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>521.6925</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>521.6133333333332</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>521.5517500000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>33.16920585491231</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>31.30505104847551</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>30.00038921290847</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>29.06625129664676</v>
-      </c>
       <c r="AW22" t="n">
-        <v>28.55579440054179</v>
+        <v>521.8845</v>
       </c>
       <c r="AX22" t="n">
-        <v>28.08497609187966</v>
+        <v>521.721</v>
       </c>
       <c r="AY22" t="n">
-        <v>27.65739177155246</v>
+        <v>521.692</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27.2431376488599</v>
+        <v>521.6135</v>
       </c>
       <c r="BA22" t="n">
-        <v>26.82872296557154</v>
+        <v>521.552</v>
       </c>
       <c r="BB22" t="n">
+        <v>33.17100000000001</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>31.3045</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>30.0015</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>29.06750000000001</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>28.5565</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>28.085</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>27.6565</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>27.2425</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>26.8295</v>
+      </c>
+      <c r="BK22" t="n">
         <v>446.1</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>443.5</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>443.45</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>443.45</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>443.45</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>443.45</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>443.1</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>443.1</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>443.1</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>634.05</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>634.3</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>634.35</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>634.8</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6284920634920635</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6850122793872794</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.5754746642246642</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6931145879404393</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7718501484132794</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8452619934264961</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7355592311256574</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8625784630810285</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8835727131372902</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>520.7634999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.485</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.313893370663573</v>
       </c>
       <c r="C23" t="n">
+        <v>2.010781290105261</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.356271980175999</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.010781290105261</v>
       </c>
       <c r="E23" t="n">
         <v>1.313893370663573</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01605910137093934</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>4.25193454423055</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2205561153085537</v>
+      </c>
       <c r="I23" t="n">
-        <v>6.591150198970384</v>
+        <v>0.2116420762066291</v>
       </c>
       <c r="J23" t="n">
-        <v>6.243037609390838</v>
+        <v>0.2135729876473885</v>
       </c>
       <c r="K23" t="n">
-        <v>5.08035778165184</v>
+        <v>0.2136961689679507</v>
       </c>
       <c r="L23" t="n">
-        <v>5.173697323027763</v>
+        <v>0.2139964338118991</v>
       </c>
       <c r="M23" t="n">
-        <v>4.024805879826182</v>
+        <v>0.221964316714955</v>
       </c>
       <c r="N23" t="n">
-        <v>4.819108665956385</v>
+        <v>0.2606525212655831</v>
       </c>
       <c r="O23" t="n">
-        <v>3.171352311573223</v>
+        <v>0.2653592401175989</v>
       </c>
       <c r="P23" t="n">
-        <v>3.869727639777928</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.485402524068921</v>
-      </c>
+        <v>0.2435288808118529</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>4.538836902004706</v>
+        <v>6.589634823361851</v>
       </c>
       <c r="S23" t="n">
-        <v>2.164197263712315</v>
+        <v>6.242814732912845</v>
       </c>
       <c r="T23" t="n">
-        <v>4.236070817647175</v>
+        <v>5.08046669530519</v>
       </c>
       <c r="U23" t="n">
-        <v>2.214569912360111</v>
+        <v>5.174413035616493</v>
       </c>
       <c r="V23" t="n">
-        <v>3.766572028184935</v>
+        <v>4.024206067497563</v>
       </c>
       <c r="W23" t="n">
-        <v>2.052549321551087</v>
+        <v>4.818427238490956</v>
       </c>
       <c r="X23" t="n">
-        <v>3.623400866042865</v>
+        <v>3.172307146475425</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.402068656034972</v>
+        <v>3.869352591026593</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.28689451810944</v>
+        <v>2.48493243580712</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.1643703429801111</v>
+        <v>4.53892927322826</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1760982473753926</v>
+        <v>2.163858639219828</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1773176879023994</v>
+        <v>4.236437182350282</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1622575273455711</v>
+        <v>2.215555710259438</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1654097266565869</v>
+        <v>3.766745908186814</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1692773176649687</v>
+        <v>2.052410905816805</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1650128641923506</v>
+        <v>3.623163019125402</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.1610449669712382</v>
+        <v>2.402560640562258</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.1627534474276786</v>
+        <v>3.286896632643657</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7.164520932858559</v>
+        <v>0.1637424164575826</v>
       </c>
       <c r="AK23" t="n">
-        <v>6.217209832345618</v>
+        <v>0.1759926732924743</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.841785425023886</v>
+        <v>0.1774816521280587</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.1624937245751841</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.166077819425904</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.1693827804583142</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.1656335524107677</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.1601799974370938</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.1639279366705158</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.165437860789956</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.216778887562426</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.842359255352168</v>
+      </c>
+      <c r="AV23" t="n">
         <v>4.095081099383292</v>
       </c>
-      <c r="AN23" t="n">
-        <v>3.787096701358255</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>3.434862864036466</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.255547896324542</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.077738404122501</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2.937231633877828</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.344745169653664</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.368060020396753</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.032327912868636</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.585107535923155</v>
-      </c>
       <c r="AW23" t="n">
-        <v>4.202545338938451</v>
+        <v>3.787342458074899</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.048862149395659</v>
+        <v>3.434893547726122</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.766956281425479</v>
+        <v>3.255399724829663</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.572438507484835</v>
+        <v>3.076579226485493</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.385648159451033</v>
+        <v>2.936484830182973</v>
       </c>
       <c r="BB23" t="n">
+        <v>6.344916655750574</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.368629615401719</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.033016543417653</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.585098145078249</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.202706239655837</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.047557418077177</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.767798847854638</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.572791736090096</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>3.384762255508618</v>
+      </c>
+      <c r="BK23" t="n">
         <v>48.95744661384382</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>47.16878985984382</v>
       </c>
-      <c r="BD23" t="n">
-        <v>47.12522511463752</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>47.12522511463752</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>47.12522511463752</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>47.12522511463752</v>
-      </c>
-      <c r="BH23" t="n">
+      <c r="BM23" t="n">
+        <v>47.12522511463753</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>47.12522511463753</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>47.12522511463753</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>47.12522511463753</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>46.84902964787391</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>46.84902964787391</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>46.84902964787391</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>24.31693150656013</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>23.32628966367528</v>
       </c>
-      <c r="BM23" t="n">
-        <v>23.12955502791772</v>
-      </c>
-      <c r="BN23" t="n">
+      <c r="BV23" t="n">
+        <v>23.12955502791771</v>
+      </c>
+      <c r="BW23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>21.38272790435259</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2546141339636064</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.3060454595539527</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.3907612842735255</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.3608156592813135</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2967400299584451</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1235501316728489</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.3343981359542993</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.09000514981037479</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.08254333124541295</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>2.402560640562258</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.286896632643657</v>
       </c>
     </row>
   </sheetData>
